--- a/6.4 Bonaire with disturbances/output/yearly_population_growth_param_0.5.xlsx
+++ b/6.4 Bonaire with disturbances/output/yearly_population_growth_param_0.5.xlsx
@@ -777,10 +777,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>11603</v>
+        <v>9899</v>
       </c>
       <c r="D2" t="n">
-        <v>100581</v>
+        <v>107797</v>
       </c>
     </row>
     <row r="3">
@@ -788,13 +788,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>304</v>
+        <v>372</v>
       </c>
       <c r="C3" t="n">
-        <v>3044</v>
+        <v>3033</v>
       </c>
       <c r="D3" t="n">
-        <v>63213</v>
+        <v>62480</v>
       </c>
     </row>
     <row r="4">
@@ -802,13 +802,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>839</v>
+        <v>946</v>
       </c>
       <c r="C4" t="n">
-        <v>5390</v>
+        <v>4964</v>
       </c>
       <c r="D4" t="n">
-        <v>22857</v>
+        <v>22938</v>
       </c>
     </row>
     <row r="5">
@@ -816,13 +816,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>735</v>
+        <v>722</v>
       </c>
       <c r="C5" t="n">
-        <v>3939</v>
+        <v>3325</v>
       </c>
       <c r="D5" t="n">
-        <v>6627</v>
+        <v>6929</v>
       </c>
     </row>
     <row r="6">
@@ -830,13 +830,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>254</v>
+        <v>226</v>
       </c>
       <c r="C6" t="n">
-        <v>1269</v>
+        <v>970</v>
       </c>
       <c r="D6" t="n">
-        <v>2868</v>
+        <v>2955</v>
       </c>
     </row>
     <row r="7">
@@ -844,13 +844,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C7" t="n">
-        <v>217</v>
+        <v>176</v>
       </c>
       <c r="D7" t="n">
-        <v>1781</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="8">
@@ -858,13 +858,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C8" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D8" t="n">
-        <v>1651</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="9">
@@ -872,13 +872,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D9" t="n">
-        <v>1362</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="10">
@@ -886,13 +886,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D10" t="n">
-        <v>1125</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="11">
@@ -900,13 +900,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D11" t="n">
-        <v>951</v>
+        <v>962</v>
       </c>
     </row>
     <row r="12">
@@ -914,13 +914,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C12" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D12" t="n">
-        <v>764</v>
+        <v>841</v>
       </c>
     </row>
     <row r="13">
@@ -928,13 +928,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D13" t="n">
-        <v>480</v>
+        <v>648</v>
       </c>
     </row>
     <row r="14">
@@ -942,13 +942,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D14" t="n">
-        <v>338</v>
+        <v>451</v>
       </c>
     </row>
     <row r="15">
@@ -956,13 +956,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>211</v>
+        <v>344</v>
       </c>
     </row>
     <row r="16">
@@ -970,13 +970,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>265</v>
       </c>
     </row>
     <row r="17">
@@ -984,13 +984,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18">
@@ -998,13 +998,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19">
@@ -1015,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -1088,10 +1088,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>16081</v>
+        <v>13598</v>
       </c>
       <c r="D2" t="n">
-        <v>89348</v>
+        <v>96189</v>
       </c>
     </row>
     <row r="3">
@@ -1099,13 +1099,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>121</v>
+        <v>155</v>
       </c>
       <c r="C3" t="n">
-        <v>6385</v>
+        <v>5544</v>
       </c>
       <c r="D3" t="n">
-        <v>63453</v>
+        <v>63656</v>
       </c>
     </row>
     <row r="4">
@@ -1113,13 +1113,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>494</v>
+        <v>580</v>
       </c>
       <c r="C4" t="n">
-        <v>4032</v>
+        <v>3915</v>
       </c>
       <c r="D4" t="n">
-        <v>27805</v>
+        <v>27555</v>
       </c>
     </row>
     <row r="5">
@@ -1127,13 +1127,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>717</v>
+        <v>747</v>
       </c>
       <c r="C5" t="n">
-        <v>4619</v>
+        <v>4026</v>
       </c>
       <c r="D5" t="n">
-        <v>8295</v>
+        <v>8649</v>
       </c>
     </row>
     <row r="6">
@@ -1141,13 +1141,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="C6" t="n">
-        <v>2512</v>
+        <v>2032</v>
       </c>
       <c r="D6" t="n">
-        <v>3257</v>
+        <v>3413</v>
       </c>
     </row>
     <row r="7">
@@ -1155,13 +1155,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="C7" t="n">
-        <v>703</v>
+        <v>518</v>
       </c>
       <c r="D7" t="n">
-        <v>1876</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="8">
@@ -1169,13 +1169,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C8" t="n">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="D8" t="n">
-        <v>1659</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="9">
@@ -1183,13 +1183,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D9" t="n">
-        <v>1388</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="10">
@@ -1197,13 +1197,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D10" t="n">
-        <v>1147</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="11">
@@ -1211,13 +1211,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D11" t="n">
-        <v>950</v>
+        <v>965</v>
       </c>
     </row>
     <row r="12">
@@ -1225,13 +1225,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D12" t="n">
-        <v>753</v>
+        <v>841</v>
       </c>
     </row>
     <row r="13">
@@ -1239,13 +1239,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D13" t="n">
-        <v>467</v>
+        <v>654</v>
       </c>
     </row>
     <row r="14">
@@ -1253,13 +1253,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D14" t="n">
-        <v>324</v>
+        <v>457</v>
       </c>
     </row>
     <row r="15">
@@ -1267,13 +1267,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>193</v>
+        <v>345</v>
       </c>
     </row>
     <row r="16">
@@ -1281,13 +1281,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D16" t="n">
-        <v>83</v>
+        <v>265</v>
       </c>
     </row>
     <row r="17">
@@ -1295,13 +1295,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D17" t="n">
-        <v>19</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18">
@@ -1309,13 +1309,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19">
@@ -1326,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -1399,10 +1399,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>12447</v>
+        <v>10648</v>
       </c>
       <c r="D2" t="n">
-        <v>158131</v>
+        <v>172940</v>
       </c>
     </row>
     <row r="3">
@@ -1410,13 +1410,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="C3" t="n">
-        <v>9693</v>
+        <v>8044</v>
       </c>
       <c r="D3" t="n">
-        <v>63002</v>
+        <v>63169</v>
       </c>
     </row>
     <row r="4">
@@ -1424,13 +1424,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>270</v>
+        <v>326</v>
       </c>
       <c r="C4" t="n">
-        <v>5100</v>
+        <v>4599</v>
       </c>
       <c r="D4" t="n">
-        <v>31408</v>
+        <v>30958</v>
       </c>
     </row>
     <row r="5">
@@ -1438,13 +1438,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>566</v>
+        <v>618</v>
       </c>
       <c r="C5" t="n">
-        <v>4246</v>
+        <v>3892</v>
       </c>
       <c r="D5" t="n">
-        <v>10370</v>
+        <v>10745</v>
       </c>
     </row>
     <row r="6">
@@ -1452,13 +1452,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="C6" t="n">
-        <v>3438</v>
+        <v>2874</v>
       </c>
       <c r="D6" t="n">
-        <v>3700</v>
+        <v>3939</v>
       </c>
     </row>
     <row r="7">
@@ -1466,13 +1466,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="C7" t="n">
-        <v>1500</v>
+        <v>1160</v>
       </c>
       <c r="D7" t="n">
-        <v>1997</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="8">
@@ -1480,13 +1480,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>381</v>
+        <v>277</v>
       </c>
       <c r="D8" t="n">
-        <v>1673</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="9">
@@ -1494,13 +1494,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="D9" t="n">
-        <v>1414</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="10">
@@ -1508,13 +1508,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D10" t="n">
-        <v>1169</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="11">
@@ -1522,13 +1522,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D11" t="n">
-        <v>949</v>
+        <v>968</v>
       </c>
     </row>
     <row r="12">
@@ -1536,13 +1536,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D12" t="n">
-        <v>737</v>
+        <v>833</v>
       </c>
     </row>
     <row r="13">
@@ -1550,13 +1550,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D13" t="n">
-        <v>455</v>
+        <v>661</v>
       </c>
     </row>
     <row r="14">
@@ -1564,13 +1564,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D14" t="n">
-        <v>310</v>
+        <v>465</v>
       </c>
     </row>
     <row r="15">
@@ -1578,13 +1578,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>176</v>
+        <v>348</v>
       </c>
     </row>
     <row r="16">
@@ -1592,13 +1592,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D16" t="n">
-        <v>70</v>
+        <v>263</v>
       </c>
     </row>
     <row r="17">
@@ -1606,13 +1606,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>14</v>
+        <v>178</v>
       </c>
     </row>
     <row r="18">
@@ -1620,13 +1620,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19">
@@ -1637,10 +1637,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -1710,10 +1710,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>15833</v>
+        <v>13175</v>
       </c>
       <c r="D2" t="n">
-        <v>148556</v>
+        <v>162517</v>
       </c>
     </row>
     <row r="3">
@@ -1721,13 +1721,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C3" t="n">
-        <v>9717</v>
+        <v>8088</v>
       </c>
       <c r="D3" t="n">
-        <v>69669</v>
+        <v>70744</v>
       </c>
     </row>
     <row r="4">
@@ -1735,13 +1735,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>146</v>
+        <v>181</v>
       </c>
       <c r="C4" t="n">
-        <v>7110</v>
+        <v>6024</v>
       </c>
       <c r="D4" t="n">
-        <v>34092</v>
+        <v>34036</v>
       </c>
     </row>
     <row r="5">
@@ -1749,13 +1749,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>406</v>
+        <v>459</v>
       </c>
       <c r="C5" t="n">
-        <v>4534</v>
+        <v>4109</v>
       </c>
       <c r="D5" t="n">
-        <v>12276</v>
+        <v>12746</v>
       </c>
     </row>
     <row r="6">
@@ -1763,13 +1763,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>518</v>
+        <v>533</v>
       </c>
       <c r="C6" t="n">
-        <v>3747</v>
+        <v>3259</v>
       </c>
       <c r="D6" t="n">
-        <v>4331</v>
+        <v>4570</v>
       </c>
     </row>
     <row r="7">
@@ -1777,13 +1777,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>345</v>
+        <v>326</v>
       </c>
       <c r="C7" t="n">
-        <v>2297</v>
+        <v>1831</v>
       </c>
       <c r="D7" t="n">
-        <v>2129</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="8">
@@ -1791,13 +1791,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="C8" t="n">
-        <v>823</v>
+        <v>605</v>
       </c>
       <c r="D8" t="n">
-        <v>1691</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="9">
@@ -1805,13 +1805,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>206</v>
+        <v>156</v>
       </c>
       <c r="D9" t="n">
-        <v>1423</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="10">
@@ -1819,13 +1819,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D10" t="n">
-        <v>1201</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="11">
@@ -1833,13 +1833,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D11" t="n">
-        <v>938</v>
+        <v>971</v>
       </c>
     </row>
     <row r="12">
@@ -1847,13 +1847,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D12" t="n">
-        <v>721</v>
+        <v>835</v>
       </c>
     </row>
     <row r="13">
@@ -1861,13 +1861,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D13" t="n">
-        <v>446</v>
+        <v>659</v>
       </c>
     </row>
     <row r="14">
@@ -1875,13 +1875,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>293</v>
+        <v>473</v>
       </c>
     </row>
     <row r="15">
@@ -1892,10 +1892,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>159</v>
+        <v>347</v>
       </c>
     </row>
     <row r="16">
@@ -1903,13 +1903,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D16" t="n">
-        <v>58</v>
+        <v>265</v>
       </c>
     </row>
     <row r="17">
@@ -1917,13 +1917,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18">
@@ -1931,13 +1931,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19">
@@ -1948,10 +1948,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
@@ -1962,7 +1962,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -2021,10 +2021,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>16925</v>
+        <v>13913</v>
       </c>
       <c r="D2" t="n">
-        <v>210421</v>
+        <v>230504</v>
       </c>
     </row>
     <row r="3">
@@ -2032,13 +2032,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>10957</v>
+        <v>8957</v>
       </c>
       <c r="D3" t="n">
-        <v>73786</v>
+        <v>75366</v>
       </c>
     </row>
     <row r="4">
@@ -2046,13 +2046,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C4" t="n">
-        <v>8088</v>
+        <v>6750</v>
       </c>
       <c r="D4" t="n">
-        <v>36812</v>
+        <v>37230</v>
       </c>
     </row>
     <row r="5">
@@ -2060,13 +2060,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>277</v>
+        <v>321</v>
       </c>
       <c r="C5" t="n">
-        <v>5503</v>
+        <v>4777</v>
       </c>
       <c r="D5" t="n">
-        <v>13997</v>
+        <v>14484</v>
       </c>
     </row>
     <row r="6">
@@ -2074,13 +2074,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>451</v>
+        <v>475</v>
       </c>
       <c r="C6" t="n">
-        <v>4024</v>
+        <v>3550</v>
       </c>
       <c r="D6" t="n">
-        <v>5007</v>
+        <v>5376</v>
       </c>
     </row>
     <row r="7">
@@ -2088,13 +2088,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="C7" t="n">
-        <v>2850</v>
+        <v>2348</v>
       </c>
       <c r="D7" t="n">
-        <v>2279</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="8">
@@ -2102,13 +2102,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="C8" t="n">
-        <v>1357</v>
+        <v>1019</v>
       </c>
       <c r="D8" t="n">
-        <v>1711</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="9">
@@ -2116,13 +2116,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C9" t="n">
-        <v>419</v>
+        <v>305</v>
       </c>
       <c r="D9" t="n">
-        <v>1442</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="10">
@@ -2130,13 +2130,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="D10" t="n">
-        <v>1206</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="11">
@@ -2144,13 +2144,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D11" t="n">
-        <v>934</v>
+        <v>962</v>
       </c>
     </row>
     <row r="12">
@@ -2158,13 +2158,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>703</v>
+        <v>837</v>
       </c>
     </row>
     <row r="13">
@@ -2172,13 +2172,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D13" t="n">
-        <v>432</v>
+        <v>657</v>
       </c>
     </row>
     <row r="14">
@@ -2186,13 +2186,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D14" t="n">
-        <v>276</v>
+        <v>480</v>
       </c>
     </row>
     <row r="15">
@@ -2203,10 +2203,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>143</v>
+        <v>347</v>
       </c>
     </row>
     <row r="16">
@@ -2214,13 +2214,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D16" t="n">
-        <v>48</v>
+        <v>267</v>
       </c>
     </row>
     <row r="17">
@@ -2228,13 +2228,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18">
@@ -2242,13 +2242,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19">
@@ -2259,10 +2259,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
@@ -2273,7 +2273,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -2329,13 +2329,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>14744</v>
+        <v>14731</v>
       </c>
       <c r="C2" t="n">
-        <v>2169</v>
+        <v>2101</v>
       </c>
       <c r="D2" t="n">
-        <v>26388</v>
+        <v>26909</v>
       </c>
     </row>
     <row r="3">
@@ -2346,10 +2346,10 @@
         <v>62</v>
       </c>
       <c r="C3" t="n">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D3" t="n">
-        <v>14444</v>
+        <v>14295</v>
       </c>
     </row>
     <row r="4">
@@ -2357,13 +2357,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C4" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D4" t="n">
-        <v>11984</v>
+        <v>11901</v>
       </c>
     </row>
     <row r="5">
@@ -2371,13 +2371,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C5" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D5" t="n">
-        <v>3493</v>
+        <v>3669</v>
       </c>
     </row>
     <row r="6">
@@ -2388,10 +2388,10 @@
         <v>115</v>
       </c>
       <c r="C6" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D6" t="n">
-        <v>2642</v>
+        <v>2594</v>
       </c>
     </row>
     <row r="7">
@@ -2399,13 +2399,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C7" t="n">
         <v>115</v>
       </c>
       <c r="D7" t="n">
-        <v>2455</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="8">
@@ -2416,10 +2416,10 @@
         <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D8" t="n">
-        <v>2228</v>
+        <v>2201</v>
       </c>
     </row>
     <row r="9">
@@ -2427,13 +2427,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C9" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D9" t="n">
-        <v>2032</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="10">
@@ -2441,13 +2441,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D10" t="n">
-        <v>1764</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="11">
@@ -2458,10 +2458,10 @@
         <v>59</v>
       </c>
       <c r="C11" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>1586</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="12">
@@ -2475,7 +2475,7 @@
         <v>63</v>
       </c>
       <c r="D12" t="n">
-        <v>1339</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="13">
@@ -2483,13 +2483,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C13" t="n">
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>1148</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="14">
@@ -2497,13 +2497,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>967</v>
+        <v>979</v>
       </c>
     </row>
     <row r="15">
@@ -2514,10 +2514,10 @@
         <v>35</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="16">
@@ -2525,13 +2525,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>703</v>
+        <v>732</v>
       </c>
     </row>
     <row r="17">
@@ -2542,10 +2542,10 @@
         <v>30</v>
       </c>
       <c r="C17" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D17" t="n">
-        <v>526</v>
+        <v>546</v>
       </c>
     </row>
     <row r="18">
@@ -2556,10 +2556,10 @@
         <v>29</v>
       </c>
       <c r="C18" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>396</v>
+        <v>428</v>
       </c>
     </row>
     <row r="19">
@@ -2567,13 +2567,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C19" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D19" t="n">
-        <v>267</v>
+        <v>303</v>
       </c>
     </row>
     <row r="20">
@@ -2584,10 +2584,10 @@
         <v>25</v>
       </c>
       <c r="C20" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>113</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21">
@@ -2595,13 +2595,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C21" t="n">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>9100</v>
+        <v>8776</v>
       </c>
       <c r="D2" t="n">
-        <v>98482</v>
+        <v>100901</v>
       </c>
     </row>
     <row r="3">
@@ -2654,13 +2654,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4515</v>
+        <v>4393</v>
       </c>
       <c r="C3" t="n">
-        <v>754</v>
+        <v>714</v>
       </c>
       <c r="D3" t="n">
-        <v>14729</v>
+        <v>14503</v>
       </c>
     </row>
     <row r="4">
@@ -2668,13 +2668,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C4" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D4" t="n">
-        <v>11832</v>
+        <v>11654</v>
       </c>
     </row>
     <row r="5">
@@ -2682,13 +2682,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C5" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D5" t="n">
-        <v>4038</v>
+        <v>4347</v>
       </c>
     </row>
     <row r="6">
@@ -2699,10 +2699,10 @@
         <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D6" t="n">
-        <v>2694</v>
+        <v>2630</v>
       </c>
     </row>
     <row r="7">
@@ -2710,13 +2710,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C7" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D7" t="n">
-        <v>2463</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="8">
@@ -2724,13 +2724,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D8" t="n">
-        <v>2233</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="9">
@@ -2738,13 +2738,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D9" t="n">
-        <v>2065</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="10">
@@ -2752,13 +2752,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C10" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D10" t="n">
-        <v>1754</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="11">
@@ -2769,10 +2769,10 @@
         <v>58</v>
       </c>
       <c r="C11" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D11" t="n">
-        <v>1581</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="12">
@@ -2783,10 +2783,10 @@
         <v>47</v>
       </c>
       <c r="C12" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D12" t="n">
-        <v>1330</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="13">
@@ -2794,13 +2794,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C13" t="n">
         <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>1133</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="14">
@@ -2808,13 +2808,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>956</v>
+        <v>979</v>
       </c>
     </row>
     <row r="15">
@@ -2825,10 +2825,10 @@
         <v>33</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D15" t="n">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="16">
@@ -2836,13 +2836,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>667</v>
+        <v>730</v>
       </c>
     </row>
     <row r="17">
@@ -2850,13 +2850,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C17" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D17" t="n">
-        <v>500</v>
+        <v>542</v>
       </c>
     </row>
     <row r="18">
@@ -2867,10 +2867,10 @@
         <v>27</v>
       </c>
       <c r="C18" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>365</v>
+        <v>428</v>
       </c>
     </row>
     <row r="19">
@@ -2878,13 +2878,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C19" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>216</v>
+        <v>300</v>
       </c>
     </row>
     <row r="20">
@@ -2892,13 +2892,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="D20" t="n">
-        <v>69</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21">
@@ -2906,13 +2906,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2951,13 +2951,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2283</v>
+        <v>2303</v>
       </c>
       <c r="C2" t="n">
-        <v>6249</v>
+        <v>6046</v>
       </c>
       <c r="D2" t="n">
-        <v>105997</v>
+        <v>108578</v>
       </c>
     </row>
     <row r="3">
@@ -2965,13 +2965,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2423</v>
+        <v>2395</v>
       </c>
       <c r="C3" t="n">
-        <v>3222</v>
+        <v>3029</v>
       </c>
       <c r="D3" t="n">
-        <v>20745</v>
+        <v>20602</v>
       </c>
     </row>
     <row r="4">
@@ -2979,13 +2979,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1469</v>
+        <v>1392</v>
       </c>
       <c r="C4" t="n">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="D4" t="n">
-        <v>11722</v>
+        <v>11461</v>
       </c>
     </row>
     <row r="5">
@@ -2993,13 +2993,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C5" t="n">
         <v>188</v>
       </c>
       <c r="D5" t="n">
-        <v>4513</v>
+        <v>4916</v>
       </c>
     </row>
     <row r="6">
@@ -3007,13 +3007,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C6" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D6" t="n">
-        <v>2779</v>
+        <v>2721</v>
       </c>
     </row>
     <row r="7">
@@ -3021,13 +3021,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C7" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D7" t="n">
-        <v>2449</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="8">
@@ -3035,13 +3035,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C8" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D8" t="n">
-        <v>2241</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="9">
@@ -3049,13 +3049,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C9" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D9" t="n">
-        <v>2119</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="10">
@@ -3063,13 +3063,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D10" t="n">
-        <v>1744</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="11">
@@ -3077,13 +3077,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C11" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D11" t="n">
-        <v>1576</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="12">
@@ -3094,10 +3094,10 @@
         <v>46</v>
       </c>
       <c r="C12" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D12" t="n">
-        <v>1321</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="13">
@@ -3105,13 +3105,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C13" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>1119</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="14">
@@ -3119,13 +3119,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>944</v>
+        <v>978</v>
       </c>
     </row>
     <row r="15">
@@ -3133,13 +3133,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D15" t="n">
-        <v>814</v>
+        <v>824</v>
       </c>
     </row>
     <row r="16">
@@ -3147,13 +3147,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>633</v>
+        <v>727</v>
       </c>
     </row>
     <row r="17">
@@ -3161,13 +3161,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C17" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D17" t="n">
-        <v>472</v>
+        <v>538</v>
       </c>
     </row>
     <row r="18">
@@ -3175,13 +3175,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C18" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D18" t="n">
-        <v>325</v>
+        <v>428</v>
       </c>
     </row>
     <row r="19">
@@ -3189,13 +3189,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="D19" t="n">
-        <v>168</v>
+        <v>297</v>
       </c>
     </row>
     <row r="20">
@@ -3203,13 +3203,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="D20" t="n">
-        <v>42</v>
+        <v>187</v>
       </c>
     </row>
     <row r="21">
@@ -3217,13 +3217,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3262,13 +3262,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>587</v>
+        <v>1173</v>
       </c>
       <c r="C2" t="n">
-        <v>11157</v>
+        <v>10479</v>
       </c>
       <c r="D2" t="n">
-        <v>176487</v>
+        <v>180763</v>
       </c>
     </row>
     <row r="3">
@@ -3276,13 +3276,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1994</v>
+        <v>1969</v>
       </c>
       <c r="C3" t="n">
-        <v>3867</v>
+        <v>3602</v>
       </c>
       <c r="D3" t="n">
-        <v>26602</v>
+        <v>26486</v>
       </c>
     </row>
     <row r="4">
@@ -3290,13 +3290,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1577</v>
+        <v>1517</v>
       </c>
       <c r="C4" t="n">
-        <v>1415</v>
+        <v>1282</v>
       </c>
       <c r="D4" t="n">
-        <v>12145</v>
+        <v>11880</v>
       </c>
     </row>
     <row r="5">
@@ -3304,13 +3304,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>496</v>
+        <v>460</v>
       </c>
       <c r="C5" t="n">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="D5" t="n">
-        <v>4929</v>
+        <v>5394</v>
       </c>
     </row>
     <row r="6">
@@ -3318,13 +3318,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C6" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D6" t="n">
-        <v>2890</v>
+        <v>2851</v>
       </c>
     </row>
     <row r="7">
@@ -3332,13 +3332,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C7" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D7" t="n">
-        <v>2440</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="8">
@@ -3346,13 +3346,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C8" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D8" t="n">
-        <v>2248</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="9">
@@ -3360,13 +3360,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D9" t="n">
-        <v>2154</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="10">
@@ -3374,13 +3374,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C10" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D10" t="n">
-        <v>1752</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="11">
@@ -3388,13 +3388,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C11" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D11" t="n">
-        <v>1570</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="12">
@@ -3405,10 +3405,10 @@
         <v>45</v>
       </c>
       <c r="C12" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D12" t="n">
-        <v>1300</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="13">
@@ -3416,13 +3416,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>1116</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="14">
@@ -3430,13 +3430,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>931</v>
+        <v>976</v>
       </c>
     </row>
     <row r="15">
@@ -3444,13 +3444,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D15" t="n">
-        <v>786</v>
+        <v>815</v>
       </c>
     </row>
     <row r="16">
@@ -3458,13 +3458,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>607</v>
+        <v>724</v>
       </c>
     </row>
     <row r="17">
@@ -3472,13 +3472,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C17" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D17" t="n">
-        <v>440</v>
+        <v>534</v>
       </c>
     </row>
     <row r="18">
@@ -3486,13 +3486,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D18" t="n">
-        <v>282</v>
+        <v>427</v>
       </c>
     </row>
     <row r="19">
@@ -3500,13 +3500,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="D19" t="n">
-        <v>127</v>
+        <v>294</v>
       </c>
     </row>
     <row r="20">
@@ -3514,13 +3514,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D20" t="n">
-        <v>25</v>
+        <v>188</v>
       </c>
     </row>
     <row r="21">
@@ -3528,13 +3528,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2512</v>
+        <v>3037</v>
       </c>
       <c r="C2" t="n">
-        <v>8266</v>
+        <v>7863</v>
       </c>
       <c r="D2" t="n">
-        <v>169303</v>
+        <v>173282</v>
       </c>
     </row>
     <row r="3">
@@ -3587,13 +3587,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1009</v>
+        <v>1169</v>
       </c>
       <c r="C3" t="n">
-        <v>5318</v>
+        <v>4823</v>
       </c>
       <c r="D3" t="n">
-        <v>35260</v>
+        <v>35271</v>
       </c>
     </row>
     <row r="4">
@@ -3601,13 +3601,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1051</v>
+        <v>1014</v>
       </c>
       <c r="C4" t="n">
-        <v>1901</v>
+        <v>1691</v>
       </c>
       <c r="D4" t="n">
-        <v>11249</v>
+        <v>11177</v>
       </c>
     </row>
     <row r="5">
@@ -3615,13 +3615,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>482</v>
+        <v>443</v>
       </c>
       <c r="C5" t="n">
-        <v>492</v>
+        <v>429</v>
       </c>
       <c r="D5" t="n">
-        <v>4340</v>
+        <v>4671</v>
       </c>
     </row>
     <row r="6">
@@ -3629,13 +3629,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D6" t="n">
-        <v>2359</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="7">
@@ -3643,13 +3643,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C7" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D7" t="n">
-        <v>1842</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="8">
@@ -3657,13 +3657,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C8" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D8" t="n">
-        <v>1663</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="9">
@@ -3671,13 +3671,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C9" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D9" t="n">
-        <v>1596</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="10">
@@ -3685,13 +3685,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D10" t="n">
-        <v>1240</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="11">
@@ -3699,13 +3699,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D11" t="n">
-        <v>1099</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="12">
@@ -3713,13 +3713,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D12" t="n">
-        <v>898</v>
+        <v>918</v>
       </c>
     </row>
     <row r="13">
@@ -3727,13 +3727,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C13" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D13" t="n">
-        <v>758</v>
+        <v>772</v>
       </c>
     </row>
     <row r="14">
@@ -3741,13 +3741,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D14" t="n">
-        <v>626</v>
+        <v>659</v>
       </c>
     </row>
     <row r="15">
@@ -3755,13 +3755,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>519</v>
+        <v>554</v>
       </c>
     </row>
     <row r="16">
@@ -3769,13 +3769,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D16" t="n">
-        <v>387</v>
+        <v>482</v>
       </c>
     </row>
     <row r="17">
@@ -3783,13 +3783,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D17" t="n">
-        <v>272</v>
+        <v>357</v>
       </c>
     </row>
     <row r="18">
@@ -3797,13 +3797,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D18" t="n">
-        <v>159</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19">
@@ -3811,13 +3811,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>62</v>
+        <v>194</v>
       </c>
     </row>
     <row r="20">
@@ -3825,13 +3825,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21">
@@ -3839,13 +3839,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -3887,10 +3887,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>7226</v>
+        <v>6787</v>
       </c>
       <c r="D2" t="n">
-        <v>183667</v>
+        <v>190348</v>
       </c>
     </row>
     <row r="3">
@@ -3898,13 +3898,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1443</v>
+        <v>1694</v>
       </c>
       <c r="C3" t="n">
-        <v>5925</v>
+        <v>5427</v>
       </c>
       <c r="D3" t="n">
-        <v>47056</v>
+        <v>47479</v>
       </c>
     </row>
     <row r="4">
@@ -3912,13 +3912,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>895</v>
+        <v>943</v>
       </c>
       <c r="C4" t="n">
-        <v>3501</v>
+        <v>3115</v>
       </c>
       <c r="D4" t="n">
-        <v>14011</v>
+        <v>13844</v>
       </c>
     </row>
     <row r="5">
@@ -3926,13 +3926,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>665</v>
+        <v>622</v>
       </c>
       <c r="C5" t="n">
-        <v>1131</v>
+        <v>965</v>
       </c>
       <c r="D5" t="n">
-        <v>4937</v>
+        <v>5233</v>
       </c>
     </row>
     <row r="6">
@@ -3940,13 +3940,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="C6" t="n">
-        <v>289</v>
+        <v>251</v>
       </c>
       <c r="D6" t="n">
-        <v>2543</v>
+        <v>2608</v>
       </c>
     </row>
     <row r="7">
@@ -3954,13 +3954,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C7" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D7" t="n">
-        <v>1863</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="8">
@@ -3968,13 +3968,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C8" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D8" t="n">
-        <v>1674</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="9">
@@ -3982,13 +3982,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C9" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D9" t="n">
-        <v>1614</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="10">
@@ -3996,13 +3996,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D10" t="n">
-        <v>1268</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="11">
@@ -4010,13 +4010,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D11" t="n">
-        <v>1099</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="12">
@@ -4024,13 +4024,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D12" t="n">
-        <v>895</v>
+        <v>912</v>
       </c>
     </row>
     <row r="13">
@@ -4038,13 +4038,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D13" t="n">
-        <v>750</v>
+        <v>775</v>
       </c>
     </row>
     <row r="14">
@@ -4052,13 +4052,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C14" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D14" t="n">
-        <v>617</v>
+        <v>653</v>
       </c>
     </row>
     <row r="15">
@@ -4066,13 +4066,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>505</v>
+        <v>555</v>
       </c>
     </row>
     <row r="16">
@@ -4080,13 +4080,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D16" t="n">
-        <v>369</v>
+        <v>476</v>
       </c>
     </row>
     <row r="17">
@@ -4094,13 +4094,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D17" t="n">
-        <v>248</v>
+        <v>360</v>
       </c>
     </row>
     <row r="18">
@@ -4108,13 +4108,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>133</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19">
@@ -4122,13 +4122,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>45</v>
+        <v>193</v>
       </c>
     </row>
     <row r="20">
@@ -4136,13 +4136,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21">
@@ -4150,13 +4150,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -4198,10 +4198,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>3930</v>
+        <v>3855</v>
       </c>
       <c r="D2" t="n">
-        <v>141065</v>
+        <v>146197</v>
       </c>
     </row>
     <row r="3">
@@ -4209,13 +4209,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1595</v>
+        <v>1845</v>
       </c>
       <c r="C3" t="n">
-        <v>7307</v>
+        <v>6815</v>
       </c>
       <c r="D3" t="n">
-        <v>53203</v>
+        <v>53797</v>
       </c>
     </row>
     <row r="4">
@@ -4223,13 +4223,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1010</v>
+        <v>976</v>
       </c>
       <c r="C4" t="n">
-        <v>4144</v>
+        <v>3459</v>
       </c>
       <c r="D4" t="n">
-        <v>13241</v>
+        <v>13173</v>
       </c>
     </row>
     <row r="5">
@@ -4237,13 +4237,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>244</v>
+        <v>218</v>
       </c>
       <c r="C5" t="n">
-        <v>815</v>
+        <v>672</v>
       </c>
       <c r="D5" t="n">
-        <v>4715</v>
+        <v>4931</v>
       </c>
     </row>
     <row r="6">
@@ -4251,13 +4251,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C6" t="n">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D6" t="n">
-        <v>2398</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="7">
@@ -4265,13 +4265,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C7" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D7" t="n">
-        <v>1640</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="8">
@@ -4279,13 +4279,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C8" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D8" t="n">
-        <v>1581</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="9">
@@ -4293,13 +4293,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>1242</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="10">
@@ -4307,13 +4307,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D10" t="n">
-        <v>1077</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="11">
@@ -4321,13 +4321,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D11" t="n">
-        <v>877</v>
+        <v>893</v>
       </c>
     </row>
     <row r="12">
@@ -4335,13 +4335,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D12" t="n">
-        <v>735</v>
+        <v>759</v>
       </c>
     </row>
     <row r="13">
@@ -4349,13 +4349,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D13" t="n">
-        <v>604</v>
+        <v>639</v>
       </c>
     </row>
     <row r="14">
@@ -4363,13 +4363,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D14" t="n">
-        <v>494</v>
+        <v>543</v>
       </c>
     </row>
     <row r="15">
@@ -4377,13 +4377,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>361</v>
+        <v>466</v>
       </c>
     </row>
     <row r="16">
@@ -4391,13 +4391,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D16" t="n">
-        <v>243</v>
+        <v>352</v>
       </c>
     </row>
     <row r="17">
@@ -4405,13 +4405,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>130</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18">
@@ -4419,13 +4419,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D18" t="n">
-        <v>44</v>
+        <v>189</v>
       </c>
     </row>
     <row r="19">
@@ -4433,13 +4433,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20">
@@ -4447,13 +4447,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
@@ -4509,10 +4509,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1776</v>
+        <v>1825</v>
       </c>
       <c r="D2" t="n">
-        <v>105347</v>
+        <v>110771</v>
       </c>
     </row>
     <row r="3">
@@ -4520,13 +4520,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>761</v>
+        <v>911</v>
       </c>
       <c r="C3" t="n">
-        <v>5205</v>
+        <v>5009</v>
       </c>
       <c r="D3" t="n">
-        <v>61255</v>
+        <v>60652</v>
       </c>
     </row>
     <row r="4">
@@ -4534,13 +4534,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1165</v>
+        <v>1225</v>
       </c>
       <c r="C4" t="n">
-        <v>5735</v>
+        <v>5034</v>
       </c>
       <c r="D4" t="n">
-        <v>17312</v>
+        <v>17705</v>
       </c>
     </row>
     <row r="5">
@@ -4548,13 +4548,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>470</v>
+        <v>429</v>
       </c>
       <c r="C5" t="n">
-        <v>2243</v>
+        <v>1787</v>
       </c>
       <c r="D5" t="n">
-        <v>5362</v>
+        <v>5587</v>
       </c>
     </row>
     <row r="6">
@@ -4562,13 +4562,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="C6" t="n">
-        <v>365</v>
+        <v>294</v>
       </c>
       <c r="D6" t="n">
-        <v>2611</v>
+        <v>2651</v>
       </c>
     </row>
     <row r="7">
@@ -4576,13 +4576,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C7" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D7" t="n">
-        <v>1712</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="8">
@@ -4590,13 +4590,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C8" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D8" t="n">
-        <v>1631</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="9">
@@ -4604,13 +4604,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D9" t="n">
-        <v>1308</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="10">
@@ -4618,13 +4618,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D10" t="n">
-        <v>1126</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="11">
@@ -4632,13 +4632,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D11" t="n">
-        <v>941</v>
+        <v>956</v>
       </c>
     </row>
     <row r="12">
@@ -4646,13 +4646,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C12" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D12" t="n">
-        <v>788</v>
+        <v>825</v>
       </c>
     </row>
     <row r="13">
@@ -4660,13 +4660,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>495</v>
+        <v>644</v>
       </c>
     </row>
     <row r="14">
@@ -4674,13 +4674,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D14" t="n">
-        <v>353</v>
+        <v>456</v>
       </c>
     </row>
     <row r="15">
@@ -4688,13 +4688,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>238</v>
+        <v>344</v>
       </c>
     </row>
     <row r="16">
@@ -4702,13 +4702,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>127</v>
+        <v>273</v>
       </c>
     </row>
     <row r="17">
@@ -4716,13 +4716,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D17" t="n">
-        <v>43</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18">
@@ -4730,13 +4730,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19">
@@ -4744,13 +4744,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
